--- a/dispatching_policy_report.xlsx
+++ b/dispatching_policy_report.xlsx
@@ -56,12 +56,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
       <color rgb="00000000"/>
       <sz val="9"/>
     </font>
@@ -91,12 +91,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DEEAF1"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DEEAF1"/>
       </patternFill>
     </fill>
     <fill>
@@ -107,11 +112,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -172,16 +172,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -212,69 +212,69 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -981,11 +981,11 @@
       </c>
       <c r="Z5" s="8" t="inlineStr">
         <is>
-          <t>no dispatch</t>
+          <t>→ lab 2</t>
         </is>
       </c>
       <c r="AA5" s="6" t="n">
-        <v>0</v>
+        <v>47.86</v>
       </c>
       <c r="AB5" s="6" t="n">
         <v>15.190181</v>
@@ -994,10 +994,10 @@
         <v>0</v>
       </c>
       <c r="AD5" s="6" t="n">
-        <v>15.1902</v>
+        <v>63.0502</v>
       </c>
       <c r="AE5" s="6" t="n">
-        <v>15.1902</v>
+        <v>63.0502</v>
       </c>
     </row>
     <row r="6" ht="13" customHeight="1">
@@ -1025,13 +1025,13 @@
         <v>1</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>2</v>
@@ -1043,13 +1043,13 @@
         <v>3</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O6" s="9" t="n">
         <v>3</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="9" t="n">
         <v>0</v>
@@ -1087,115 +1087,115 @@
         <v>0</v>
       </c>
       <c r="AB6" s="10" t="n">
-        <v>15.797788</v>
+        <v>12.759752</v>
       </c>
       <c r="AC6" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD6" s="10" t="n">
-        <v>15.7978</v>
+        <v>12.7598</v>
       </c>
       <c r="AE6" s="10" t="n">
-        <v>30.988</v>
+        <v>75.8099</v>
       </c>
     </row>
     <row r="7" ht="13" customHeight="1">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6" t="n">
+      <c r="B7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="14" t="n">
         <v>6.7848</v>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>arrive a3</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5" t="n">
+      <c r="E7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5" t="n">
+      <c r="M7" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" s="5" t="n">
+      <c r="N7" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="O7" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="M7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="8" t="inlineStr">
+      <c r="P7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="16" t="inlineStr">
         <is>
           <t>no dispatch</t>
         </is>
       </c>
-      <c r="AA7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="6" t="n">
-        <v>16.405396</v>
-      </c>
-      <c r="AC7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="6" t="n">
-        <v>16.4054</v>
-      </c>
-      <c r="AE7" s="6" t="n">
-        <v>47.3934</v>
+      <c r="AA7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="14" t="n">
+        <v>13.367359</v>
+      </c>
+      <c r="AC7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="14" t="n">
+        <v>13.3674</v>
+      </c>
+      <c r="AE7" s="14" t="n">
+        <v>89.1773</v>
       </c>
     </row>
     <row r="8" ht="13" customHeight="1">
@@ -1223,13 +1223,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>4</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>2</v>
@@ -1241,13 +1241,13 @@
         <v>3</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O8" s="9" t="n">
         <v>3</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="9" t="n">
         <v>0</v>
@@ -1285,16 +1285,16 @@
         <v>0</v>
       </c>
       <c r="AB8" s="10" t="n">
-        <v>17.013003</v>
+        <v>13.974967</v>
       </c>
       <c r="AC8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD8" s="10" t="n">
-        <v>17.013</v>
+        <v>13.975</v>
       </c>
       <c r="AE8" s="10" t="n">
-        <v>64.4064</v>
+        <v>103.1523</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1">
@@ -1322,13 +1322,13 @@
         <v>1</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>2</v>
@@ -1340,13 +1340,13 @@
         <v>3</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O9" s="5" t="n">
         <v>3</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1377,23 +1377,23 @@
       </c>
       <c r="Z9" s="8" t="inlineStr">
         <is>
-          <t>no dispatch</t>
+          <t>→ lab 1</t>
         </is>
       </c>
       <c r="AA9" s="6" t="n">
-        <v>0</v>
+        <v>146.81</v>
       </c>
       <c r="AB9" s="6" t="n">
-        <v>17.62061</v>
+        <v>14.582574</v>
       </c>
       <c r="AC9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="AD9" s="6" t="n">
-        <v>17.6206</v>
+        <v>161.3926</v>
       </c>
       <c r="AE9" s="6" t="n">
-        <v>82.027</v>
+        <v>264.5448</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1">
@@ -1421,13 +1421,13 @@
         <v>1</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>2</v>
@@ -1436,16 +1436,16 @@
         <v>3</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N10" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O10" s="9" t="n">
         <v>3</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="9" t="n">
         <v>0</v>
@@ -1483,115 +1483,115 @@
         <v>0</v>
       </c>
       <c r="AB10" s="10" t="n">
-        <v>18.228217</v>
+        <v>13.974967</v>
       </c>
       <c r="AC10" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD10" s="10" t="n">
-        <v>18.2282</v>
+        <v>13.975</v>
       </c>
       <c r="AE10" s="10" t="n">
-        <v>100.2552</v>
+        <v>278.5198</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="6" t="n">
+      <c r="B11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14" t="n">
         <v>4.3544</v>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>arrive a3</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="5" t="n">
+      <c r="E11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="5" t="n">
+      <c r="M11" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" s="5" t="n">
+      <c r="N11" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="O11" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="M11" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="8" t="inlineStr">
+      <c r="P11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="16" t="inlineStr">
         <is>
           <t>no dispatch</t>
         </is>
       </c>
-      <c r="AA11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="6" t="n">
-        <v>18.835825</v>
-      </c>
-      <c r="AC11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="6" t="n">
-        <v>18.8358</v>
-      </c>
-      <c r="AE11" s="6" t="n">
-        <v>119.091</v>
+      <c r="AA11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="14" t="n">
+        <v>14.582574</v>
+      </c>
+      <c r="AC11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="14" t="n">
+        <v>14.5826</v>
+      </c>
+      <c r="AE11" s="14" t="n">
+        <v>293.1024</v>
       </c>
     </row>
     <row r="12" ht="13" customHeight="1">
@@ -1619,13 +1619,13 @@
         <v>1</v>
       </c>
       <c r="H12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>7</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>2</v>
@@ -1634,16 +1634,16 @@
         <v>3</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N12" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O12" s="9" t="n">
         <v>3</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="9" t="n">
         <v>0</v>
@@ -1681,115 +1681,115 @@
         <v>0</v>
       </c>
       <c r="AB12" s="10" t="n">
-        <v>18.835825</v>
+        <v>15.190181</v>
       </c>
       <c r="AC12" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD12" s="10" t="n">
-        <v>18.8358</v>
+        <v>15.1902</v>
       </c>
       <c r="AE12" s="10" t="n">
-        <v>137.9268</v>
+        <v>308.2926</v>
       </c>
     </row>
     <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="6" t="n">
+      <c r="B13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="14" t="n">
         <v>3.1391</v>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>proc L2</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="5" t="n">
+      <c r="E13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5" t="n">
+      <c r="M13" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" s="5" t="n">
+      <c r="N13" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="O13" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="M13" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="8" t="inlineStr">
+      <c r="P13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="16" t="inlineStr">
         <is>
           <t>no dispatch</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="6" t="n">
-        <v>18.835825</v>
-      </c>
-      <c r="AC13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="6" t="n">
-        <v>18.8358</v>
-      </c>
-      <c r="AE13" s="6" t="n">
-        <v>156.7627</v>
+      <c r="AA13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="14" t="n">
+        <v>15.797788</v>
+      </c>
+      <c r="AC13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="14" t="n">
+        <v>15.7978</v>
+      </c>
+      <c r="AE13" s="14" t="n">
+        <v>324.0903</v>
       </c>
     </row>
     <row r="14" ht="13" customHeight="1">
@@ -1817,13 +1817,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>2</v>
@@ -1832,16 +1832,16 @@
         <v>3</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O14" s="9" t="n">
         <v>3</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="9" t="n">
         <v>0</v>
@@ -1879,115 +1879,115 @@
         <v>0</v>
       </c>
       <c r="AB14" s="10" t="n">
-        <v>17.924414</v>
+        <v>14.886377</v>
       </c>
       <c r="AC14" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD14" s="10" t="n">
-        <v>17.9244</v>
+        <v>14.8864</v>
       </c>
       <c r="AE14" s="10" t="n">
-        <v>174.6871</v>
+        <v>338.9767</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="6" t="n">
+      <c r="B15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="14" t="n">
         <v>1.9239</v>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>proc L2</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="5" t="n">
+      <c r="E15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="5" t="n">
+      <c r="M15" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="5" t="n">
+      <c r="N15" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="O15" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="M15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="8" t="inlineStr">
+      <c r="P15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="16" t="inlineStr">
         <is>
           <t>no dispatch</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="6" t="n">
-        <v>17.013003</v>
-      </c>
-      <c r="AC15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="6" t="n">
-        <v>17.013</v>
-      </c>
-      <c r="AE15" s="6" t="n">
-        <v>191.7001</v>
+      <c r="AA15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="14" t="n">
+        <v>13.974967</v>
+      </c>
+      <c r="AC15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="14" t="n">
+        <v>13.975</v>
+      </c>
+      <c r="AE15" s="14" t="n">
+        <v>352.9517</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1">
@@ -2015,13 +2015,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>1</v>
@@ -2030,16 +2030,16 @@
         <v>3</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N16" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O16" s="9" t="n">
         <v>3</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>0</v>
@@ -2077,412 +2077,412 @@
         <v>0</v>
       </c>
       <c r="AB16" s="10" t="n">
-        <v>16.101592</v>
+        <v>13.063556</v>
       </c>
       <c r="AC16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD16" s="10" t="n">
-        <v>16.1016</v>
+        <v>13.0636</v>
       </c>
       <c r="AE16" s="10" t="n">
-        <v>207.8017</v>
+        <v>366.0152</v>
       </c>
     </row>
     <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="6" t="n">
+      <c r="B17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="14" t="n">
         <v>0.7087</v>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>proc L2</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="5" t="n">
+      <c r="E17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="5" t="n">
+      <c r="M17" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="K17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="5" t="n">
+      <c r="N17" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="O17" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="M17" s="5" t="n">
+      <c r="P17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="16" t="inlineStr">
+        <is>
+          <t>no dispatch</t>
+        </is>
+      </c>
+      <c r="AA17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="14" t="n">
+        <v>12.152145</v>
+      </c>
+      <c r="AC17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="14" t="n">
+        <v>12.1521</v>
+      </c>
+      <c r="AE17" s="14" t="n">
+        <v>378.1674</v>
+      </c>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>0.1011</v>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>proc L2</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="N17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" s="5" t="n">
+      <c r="M18" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="N18" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="P17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="8" t="inlineStr">
+      <c r="O18" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z18" s="20" t="inlineStr">
+        <is>
+          <t>→ lab 2</t>
+        </is>
+      </c>
+      <c r="AA18" s="18" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="AB18" s="18" t="n">
+        <v>11.240734</v>
+      </c>
+      <c r="AC18" s="18" t="n">
+        <v>200000</v>
+      </c>
+      <c r="AD18" s="18" t="n">
+        <v>200059.1007</v>
+      </c>
+      <c r="AE18" s="18" t="n">
+        <v>200437.2681</v>
+      </c>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>arrive a3</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="M19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="P19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="24" t="inlineStr">
         <is>
           <t>no dispatch</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="6" t="n">
-        <v>15.190181</v>
-      </c>
-      <c r="AC17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="6" t="n">
-        <v>15.1902</v>
-      </c>
-      <c r="AE17" s="6" t="n">
-        <v>222.9919</v>
-      </c>
-    </row>
-    <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="B18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>0.1011</v>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>proc L2</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="13" t="n">
+      <c r="AA19" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="22" t="n">
+        <v>12.759752</v>
+      </c>
+      <c r="AC19" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="22" t="n">
+        <v>12.7598</v>
+      </c>
+      <c r="AE19" s="22" t="n">
+        <v>200450.0279</v>
+      </c>
+    </row>
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>7.3924</v>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>arrive a3</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="I18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="13" t="n">
+      <c r="L20" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="K18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="13" t="n">
+      <c r="M20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="M18" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="N18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="P18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="16" t="inlineStr">
-        <is>
-          <t>→ lab 1</t>
-        </is>
-      </c>
-      <c r="AA18" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="14" t="n">
-        <v>14.27877</v>
-      </c>
-      <c r="AC18" s="14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD18" s="14" t="n">
-        <v>19.7788</v>
-      </c>
-      <c r="AE18" s="14" t="n">
-        <v>242.7706</v>
-      </c>
-    </row>
-    <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B19" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>arrive a3</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="M19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="O19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="20" t="inlineStr">
+      <c r="O20" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="12" t="inlineStr">
         <is>
           <t>no dispatch</t>
         </is>
       </c>
-      <c r="AA19" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="18" t="n">
-        <v>8.810305</v>
-      </c>
-      <c r="AC19" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="18" t="n">
-        <v>8.8103</v>
-      </c>
-      <c r="AE19" s="18" t="n">
-        <v>251.5809</v>
-      </c>
-    </row>
-    <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="21" t="n">
-        <v>15</v>
-      </c>
-      <c r="B20" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="22" t="n">
-        <v>7.3924</v>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>arrive a3</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="M20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="O20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="24" t="inlineStr">
-        <is>
-          <t>→ lab 2</t>
-        </is>
-      </c>
-      <c r="AA20" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="22" t="n">
-        <v>9.417911999999999</v>
-      </c>
-      <c r="AC20" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="22" t="n">
-        <v>10.4179</v>
-      </c>
-      <c r="AE20" s="22" t="n">
-        <v>261.9988</v>
+      <c r="AA20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="10" t="n">
+        <v>13.367359</v>
+      </c>
+      <c r="AC20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="10" t="n">
+        <v>13.3674</v>
+      </c>
+      <c r="AE20" s="10" t="n">
+        <v>200463.3952</v>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1">
@@ -2516,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" s="21" t="n">
         <v>3</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="N21" s="21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O21" s="21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P21" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="21" t="n">
         <v>0</v>
@@ -2565,23 +2565,23 @@
       </c>
       <c r="Z21" s="24" t="inlineStr">
         <is>
-          <t>→ lab 2</t>
+          <t>no dispatch</t>
         </is>
       </c>
       <c r="AA21" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="22" t="n">
-        <v>9.721716000000001</v>
+        <v>13.974967</v>
       </c>
       <c r="AC21" s="22" t="n">
         <v>0</v>
       </c>
       <c r="AD21" s="22" t="n">
-        <v>10.7217</v>
+        <v>13.975</v>
       </c>
       <c r="AE21" s="22" t="n">
-        <v>272.7206</v>
+        <v>200477.3702</v>
       </c>
     </row>
     <row r="22" ht="13" customHeight="1">
@@ -2615,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>2</v>
@@ -2627,13 +2627,13 @@
         <v>0</v>
       </c>
       <c r="N22" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="9" t="n">
         <v>0</v>
@@ -2671,16 +2671,16 @@
         <v>0</v>
       </c>
       <c r="AB22" s="10" t="n">
-        <v>8.506501</v>
+        <v>13.063556</v>
       </c>
       <c r="AC22" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD22" s="10" t="n">
-        <v>8.506500000000001</v>
+        <v>13.0636</v>
       </c>
       <c r="AE22" s="10" t="n">
-        <v>281.2271</v>
+        <v>200490.4338</v>
       </c>
     </row>
     <row r="23" ht="13" customHeight="1">
@@ -2714,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="J23" s="21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K23" s="21" t="n">
         <v>2</v>
@@ -2726,13 +2726,13 @@
         <v>0</v>
       </c>
       <c r="N23" s="21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O23" s="21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P23" s="21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="21" t="n">
         <v>0</v>
@@ -2763,23 +2763,23 @@
       </c>
       <c r="Z23" s="24" t="inlineStr">
         <is>
-          <t>→ lab 2</t>
+          <t>no dispatch</t>
         </is>
       </c>
       <c r="AA23" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="22" t="n">
-        <v>9.114108999999999</v>
+        <v>13.671163</v>
       </c>
       <c r="AC23" s="22" t="n">
         <v>0</v>
       </c>
       <c r="AD23" s="22" t="n">
-        <v>10.1141</v>
+        <v>13.6712</v>
       </c>
       <c r="AE23" s="22" t="n">
-        <v>291.3412</v>
+        <v>200504.1049</v>
       </c>
     </row>
     <row r="24" ht="13" customHeight="1">
@@ -2813,7 +2813,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>1</v>
@@ -2825,159 +2825,159 @@
         <v>0</v>
       </c>
       <c r="N24" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="12" t="inlineStr">
+        <is>
+          <t>no dispatch</t>
+        </is>
+      </c>
+      <c r="AA24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="10" t="n">
+        <v>12.759752</v>
+      </c>
+      <c r="AC24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="10" t="n">
+        <v>12.7598</v>
+      </c>
+      <c r="AE24" s="10" t="n">
+        <v>200516.8647</v>
+      </c>
+    </row>
+    <row r="25" ht="13" customHeight="1">
+      <c r="A25" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="22" t="n">
+        <v>4.3544</v>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>arrive a3</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="Q24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="12" t="inlineStr">
+      <c r="K25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="M25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="P25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="24" t="inlineStr">
         <is>
           <t>no dispatch</t>
         </is>
       </c>
-      <c r="AA24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="10" t="n">
-        <v>7.898894</v>
-      </c>
-      <c r="AC24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="10" t="n">
-        <v>7.8989</v>
-      </c>
-      <c r="AE24" s="10" t="n">
-        <v>299.2401</v>
-      </c>
-    </row>
-    <row r="25" ht="13" customHeight="1">
-      <c r="A25" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="B25" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="18" t="n">
-        <v>4.3544</v>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>arrive a3</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="M25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="O25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="20" t="inlineStr">
-        <is>
-          <t>no dispatch</t>
-        </is>
-      </c>
-      <c r="AA25" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="18" t="n">
-        <v>6.987483</v>
-      </c>
-      <c r="AC25" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" s="18" t="n">
-        <v>6.9875</v>
-      </c>
-      <c r="AE25" s="18" t="n">
-        <v>306.2276</v>
+      <c r="AA25" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="22" t="n">
+        <v>11.848341</v>
+      </c>
+      <c r="AC25" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="22" t="n">
+        <v>11.8483</v>
+      </c>
+      <c r="AE25" s="22" t="n">
+        <v>200528.713</v>
       </c>
     </row>
     <row r="26" ht="13" customHeight="1">
@@ -3011,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>0</v>
@@ -3023,13 +3023,13 @@
         <v>0</v>
       </c>
       <c r="N26" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O26" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P26" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="9" t="n">
         <v>0</v>
@@ -3044,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="U26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3067,16 +3067,16 @@
         <v>0</v>
       </c>
       <c r="AB26" s="10" t="n">
-        <v>7.595091</v>
+        <v>12.455948</v>
       </c>
       <c r="AC26" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD26" s="10" t="n">
-        <v>7.5951</v>
+        <v>12.4559</v>
       </c>
       <c r="AE26" s="10" t="n">
-        <v>313.8226</v>
+        <v>200541.169</v>
       </c>
     </row>
     <row r="27" ht="13" customHeight="1">
@@ -3110,7 +3110,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K27" s="21" t="n">
         <v>0</v>
@@ -3122,13 +3122,13 @@
         <v>0</v>
       </c>
       <c r="N27" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O27" s="21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P27" s="21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="21" t="n">
         <v>0</v>
@@ -3159,23 +3159,23 @@
       </c>
       <c r="Z27" s="24" t="inlineStr">
         <is>
-          <t>→ lab 2</t>
+          <t>no dispatch</t>
         </is>
       </c>
       <c r="AA27" s="22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB27" s="22" t="n">
-        <v>6.68368</v>
+        <v>11.544538</v>
       </c>
       <c r="AC27" s="22" t="n">
         <v>0</v>
       </c>
       <c r="AD27" s="22" t="n">
-        <v>7.6837</v>
+        <v>11.5445</v>
       </c>
       <c r="AE27" s="22" t="n">
-        <v>321.5063</v>
+        <v>200552.7135</v>
       </c>
     </row>
     <row r="28" ht="13" customHeight="1">
@@ -3209,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
@@ -3221,13 +3221,13 @@
         <v>0</v>
       </c>
       <c r="N28" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>0</v>
@@ -3265,115 +3265,115 @@
         <v>0</v>
       </c>
       <c r="AB28" s="10" t="n">
-        <v>6.987483</v>
+        <v>12.152145</v>
       </c>
       <c r="AC28" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD28" s="10" t="n">
-        <v>6.9875</v>
+        <v>12.1521</v>
       </c>
       <c r="AE28" s="10" t="n">
-        <v>328.4938</v>
+        <v>200564.8656</v>
       </c>
     </row>
     <row r="29" ht="13" customHeight="1">
-      <c r="A29" s="17" t="n">
+      <c r="A29" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="18" t="n">
+      <c r="B29" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="22" t="n">
         <v>1.9239</v>
       </c>
-      <c r="D29" s="19" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>arrive a3</t>
         </is>
       </c>
-      <c r="E29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="17" t="n">
+      <c r="E29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="M29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="M29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="20" t="inlineStr">
+      <c r="O29" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="P29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="24" t="inlineStr">
         <is>
           <t>no dispatch</t>
         </is>
       </c>
-      <c r="AA29" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="18" t="n">
-        <v>7.595091</v>
-      </c>
-      <c r="AC29" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="18" t="n">
-        <v>7.5951</v>
-      </c>
-      <c r="AE29" s="18" t="n">
-        <v>336.0889</v>
+      <c r="AA29" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="22" t="n">
+        <v>12.759752</v>
+      </c>
+      <c r="AC29" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="22" t="n">
+        <v>12.7598</v>
+      </c>
+      <c r="AE29" s="22" t="n">
+        <v>200577.6254</v>
       </c>
     </row>
     <row r="30" ht="13" customHeight="1">
@@ -3407,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0</v>
@@ -3419,13 +3419,13 @@
         <v>0</v>
       </c>
       <c r="N30" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P30" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="9" t="n">
         <v>0</v>
@@ -3440,10 +3440,10 @@
         <v>0</v>
       </c>
       <c r="U30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -3463,16 +3463,16 @@
         <v>0</v>
       </c>
       <c r="AB30" s="10" t="n">
-        <v>8.202698</v>
+        <v>13.367359</v>
       </c>
       <c r="AC30" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD30" s="10" t="n">
-        <v>8.2027</v>
+        <v>13.3674</v>
       </c>
       <c r="AE30" s="10" t="n">
-        <v>344.2916</v>
+        <v>200590.9928</v>
       </c>
     </row>
     <row r="31" ht="13" customHeight="1">
@@ -3506,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="21" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K31" s="21" t="n">
         <v>0</v>
@@ -3518,13 +3518,13 @@
         <v>0</v>
       </c>
       <c r="N31" s="21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P31" s="21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="21" t="n">
         <v>0</v>
@@ -3555,122 +3555,122 @@
       </c>
       <c r="Z31" s="24" t="inlineStr">
         <is>
+          <t>no dispatch</t>
+        </is>
+      </c>
+      <c r="AA31" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="22" t="n">
+        <v>12.455948</v>
+      </c>
+      <c r="AC31" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="22" t="n">
+        <v>12.4559</v>
+      </c>
+      <c r="AE31" s="22" t="n">
+        <v>200603.4487</v>
+      </c>
+    </row>
+    <row r="32" ht="13" customHeight="1">
+      <c r="A32" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>0.1011</v>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>proc L1</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="K32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="P32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="20" t="inlineStr">
+        <is>
           <t>→ lab 2</t>
         </is>
       </c>
-      <c r="AA31" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB31" s="22" t="n">
-        <v>7.291287</v>
-      </c>
-      <c r="AC31" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" s="22" t="n">
-        <v>8.2913</v>
-      </c>
-      <c r="AE31" s="22" t="n">
-        <v>352.5829</v>
-      </c>
-    </row>
-    <row r="32" ht="13" customHeight="1">
-      <c r="A32" s="13" t="n">
-        <v>27</v>
-      </c>
-      <c r="B32" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>0.1011</v>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>proc L1</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="M32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="16" t="inlineStr">
-        <is>
-          <t>no dispatch</t>
-        </is>
-      </c>
-      <c r="AA32" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="14" t="n">
-        <v>5.772269</v>
-      </c>
-      <c r="AC32" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="14" t="n">
-        <v>5.7723</v>
-      </c>
-      <c r="AE32" s="14" t="n">
-        <v>358.3551</v>
+      <c r="AA32" s="18" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="AB32" s="18" t="n">
+        <v>11.848341</v>
+      </c>
+      <c r="AC32" s="18" t="n">
+        <v>100000</v>
+      </c>
+      <c r="AD32" s="18" t="n">
+        <v>100059.7083</v>
+      </c>
+      <c r="AE32" s="18" t="n">
+        <v>300663.157</v>
       </c>
     </row>
     <row r="33" ht="13" customHeight="1">
@@ -3716,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O33" s="25" t="n">
         <v>7</v>
@@ -3760,412 +3760,412 @@
         <v>0</v>
       </c>
       <c r="AB33" s="26" t="n">
-        <v>8.810305</v>
+        <v>13.367359</v>
       </c>
       <c r="AC33" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AD33" s="26" t="n">
-        <v>8.8103</v>
+        <v>13.3674</v>
       </c>
       <c r="AE33" s="26" t="n">
-        <v>367.1655</v>
+        <v>300676.5244</v>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1">
-      <c r="A34" s="21" t="n">
+      <c r="A34" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B34" s="21" t="n">
+      <c r="B34" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C34" s="22" t="n">
+      <c r="C34" s="10" t="n">
         <v>7.3924</v>
       </c>
-      <c r="D34" s="23" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>arrive a3</t>
         </is>
       </c>
-      <c r="E34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" s="21" t="n">
+      <c r="E34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="L34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="21" t="n">
+      <c r="L34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O34" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="P34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="24" t="inlineStr">
+      <c r="P34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="12" t="inlineStr">
+        <is>
+          <t>no dispatch</t>
+        </is>
+      </c>
+      <c r="AA34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="10" t="n">
+        <v>13.974967</v>
+      </c>
+      <c r="AC34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="10" t="n">
+        <v>13.975</v>
+      </c>
+      <c r="AE34" s="10" t="n">
+        <v>300690.4994</v>
+      </c>
+    </row>
+    <row r="35" ht="13" customHeight="1">
+      <c r="A35" s="25" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" s="26" t="n">
+        <v>6.7848</v>
+      </c>
+      <c r="D35" s="27" t="inlineStr">
+        <is>
+          <t>arrive a3</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="L35" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="25" t="n">
+        <v>5</v>
+      </c>
+      <c r="O35" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="P35" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="28" t="inlineStr">
+        <is>
+          <t>no dispatch</t>
+        </is>
+      </c>
+      <c r="AA35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="26" t="n">
+        <v>14.582574</v>
+      </c>
+      <c r="AC35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="26" t="n">
+        <v>14.5826</v>
+      </c>
+      <c r="AE35" s="26" t="n">
+        <v>300705.0819</v>
+      </c>
+    </row>
+    <row r="36" ht="13" customHeight="1">
+      <c r="A36" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v>6.1772</v>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>arrive a3</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O36" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="P36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="12" t="inlineStr">
+        <is>
+          <t>no dispatch</t>
+        </is>
+      </c>
+      <c r="AA36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="10" t="n">
+        <v>15.190181</v>
+      </c>
+      <c r="AC36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="10" t="n">
+        <v>15.1902</v>
+      </c>
+      <c r="AE36" s="10" t="n">
+        <v>300720.2721</v>
+      </c>
+    </row>
+    <row r="37" ht="13" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>5.5696</v>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>proc L1</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="8" t="inlineStr">
         <is>
           <t>→ lab 1</t>
         </is>
       </c>
-      <c r="AA34" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB34" s="22" t="n">
-        <v>9.417911999999999</v>
-      </c>
-      <c r="AC34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="22" t="n">
-        <v>10.4179</v>
-      </c>
-      <c r="AE34" s="22" t="n">
-        <v>377.5834</v>
-      </c>
-    </row>
-    <row r="35" ht="13" customHeight="1">
-      <c r="A35" s="21" t="n">
-        <v>30</v>
-      </c>
-      <c r="B35" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C35" s="22" t="n">
-        <v>6.7848</v>
-      </c>
-      <c r="D35" s="23" t="inlineStr">
-        <is>
-          <t>arrive a3</t>
-        </is>
-      </c>
-      <c r="E35" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L35" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="P35" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="24" t="inlineStr">
-        <is>
-          <t>→ lab 1</t>
-        </is>
-      </c>
-      <c r="AA35" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB35" s="22" t="n">
-        <v>9.721716000000001</v>
-      </c>
-      <c r="AC35" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" s="22" t="n">
-        <v>10.7217</v>
-      </c>
-      <c r="AE35" s="22" t="n">
-        <v>388.3051</v>
-      </c>
-    </row>
-    <row r="36" ht="13" customHeight="1">
-      <c r="A36" s="21" t="n">
-        <v>31</v>
-      </c>
-      <c r="B36" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C36" s="22" t="n">
-        <v>6.1772</v>
-      </c>
-      <c r="D36" s="23" t="inlineStr">
-        <is>
-          <t>arrive a3</t>
-        </is>
-      </c>
-      <c r="E36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="N36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="P36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="24" t="inlineStr">
-        <is>
-          <t>→ lab 1</t>
-        </is>
-      </c>
-      <c r="AA36" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB36" s="22" t="n">
-        <v>10.02552</v>
-      </c>
-      <c r="AC36" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="22" t="n">
-        <v>11.0255</v>
-      </c>
-      <c r="AE36" s="22" t="n">
-        <v>399.3306</v>
-      </c>
-    </row>
-    <row r="37" ht="13" customHeight="1">
-      <c r="A37" s="21" t="n">
-        <v>32</v>
-      </c>
-      <c r="B37" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C37" s="22" t="n">
-        <v>5.5696</v>
-      </c>
-      <c r="D37" s="23" t="inlineStr">
-        <is>
-          <t>proc L1</t>
-        </is>
-      </c>
-      <c r="E37" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L37" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="N37" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="P37" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T37" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="24" t="inlineStr">
-        <is>
-          <t>→ lab 1</t>
-        </is>
-      </c>
-      <c r="AA37" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB37" s="22" t="n">
-        <v>10.329323</v>
-      </c>
-      <c r="AC37" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" s="22" t="n">
-        <v>11.3293</v>
-      </c>
-      <c r="AE37" s="22" t="n">
-        <v>410.6599</v>
+      <c r="AA37" s="6" t="n">
+        <v>146.81</v>
+      </c>
+      <c r="AB37" s="6" t="n">
+        <v>15.797788</v>
+      </c>
+      <c r="AC37" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="6" t="n">
+        <v>162.6078</v>
+      </c>
+      <c r="AE37" s="6" t="n">
+        <v>300882.8799</v>
       </c>
     </row>
     <row r="38" ht="13" customHeight="1">
@@ -4211,7 +4211,7 @@
         <v>4</v>
       </c>
       <c r="N38" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O38" s="9" t="n">
         <v>7</v>
@@ -4255,16 +4255,16 @@
         <v>0</v>
       </c>
       <c r="AB38" s="10" t="n">
-        <v>9.114108999999999</v>
+        <v>13.671163</v>
       </c>
       <c r="AC38" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD38" s="10" t="n">
-        <v>9.114100000000001</v>
+        <v>13.6712</v>
       </c>
       <c r="AE38" s="10" t="n">
-        <v>419.774</v>
+        <v>300896.5511</v>
       </c>
     </row>
     <row r="39" ht="13" customHeight="1">
@@ -4310,10 +4310,10 @@
         <v>4</v>
       </c>
       <c r="N39" s="25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O39" s="25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P39" s="25" t="n">
         <v>0</v>
@@ -4354,16 +4354,16 @@
         <v>0</v>
       </c>
       <c r="AB39" s="26" t="n">
-        <v>8.506501</v>
+        <v>12.759752</v>
       </c>
       <c r="AC39" s="26" t="n">
         <v>0</v>
       </c>
       <c r="AD39" s="26" t="n">
-        <v>8.506500000000001</v>
+        <v>12.7598</v>
       </c>
       <c r="AE39" s="26" t="n">
-        <v>428.2805</v>
+        <v>300909.3108</v>
       </c>
     </row>
     <row r="40" ht="13" customHeight="1">
@@ -4409,10 +4409,10 @@
         <v>4</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P40" s="9" t="n">
         <v>0</v>
@@ -4453,115 +4453,115 @@
         <v>0</v>
       </c>
       <c r="AB40" s="10" t="n">
-        <v>7.898894</v>
+        <v>11.848341</v>
       </c>
       <c r="AC40" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD40" s="10" t="n">
-        <v>7.8989</v>
+        <v>11.8483</v>
       </c>
       <c r="AE40" s="10" t="n">
-        <v>436.1794</v>
+        <v>300921.1592</v>
       </c>
     </row>
     <row r="41" ht="13" customHeight="1">
-      <c r="A41" s="21" t="n">
+      <c r="A41" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="B41" s="21" t="n">
+      <c r="B41" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="22" t="n">
+      <c r="C41" s="26" t="n">
         <v>3.1391</v>
       </c>
-      <c r="D41" s="23" t="inlineStr">
+      <c r="D41" s="27" t="inlineStr">
         <is>
           <t>arrive a3</t>
         </is>
       </c>
-      <c r="E41" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" s="21" t="n">
+      <c r="E41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="L41" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="21" t="n">
+      <c r="L41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="N41" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="P41" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="24" t="inlineStr">
-        <is>
-          <t>→ lab 2</t>
-        </is>
-      </c>
-      <c r="AA41" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB41" s="22" t="n">
-        <v>8.506501</v>
-      </c>
-      <c r="AC41" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" s="22" t="n">
-        <v>9.506500000000001</v>
-      </c>
-      <c r="AE41" s="22" t="n">
-        <v>445.6859</v>
+      <c r="N41" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O41" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="P41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="28" t="inlineStr">
+        <is>
+          <t>no dispatch</t>
+        </is>
+      </c>
+      <c r="AA41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="26" t="n">
+        <v>12.455948</v>
+      </c>
+      <c r="AC41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="26" t="n">
+        <v>12.4559</v>
+      </c>
+      <c r="AE41" s="26" t="n">
+        <v>300933.6151</v>
       </c>
     </row>
     <row r="42" ht="13" customHeight="1">
@@ -4595,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>4</v>
@@ -4607,13 +4607,13 @@
         <v>4</v>
       </c>
       <c r="N42" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P42" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="9" t="n">
         <v>0</v>
@@ -4628,10 +4628,10 @@
         <v>0</v>
       </c>
       <c r="U42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -4651,115 +4651,115 @@
         <v>0</v>
       </c>
       <c r="AB42" s="10" t="n">
-        <v>8.810305</v>
+        <v>13.063556</v>
       </c>
       <c r="AC42" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD42" s="10" t="n">
-        <v>8.8103</v>
+        <v>13.0636</v>
       </c>
       <c r="AE42" s="10" t="n">
-        <v>454.4962</v>
+        <v>300946.6787</v>
       </c>
     </row>
     <row r="43" ht="13" customHeight="1">
-      <c r="A43" s="21" t="n">
+      <c r="A43" s="25" t="n">
         <v>38</v>
       </c>
-      <c r="B43" s="21" t="n">
+      <c r="B43" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="C43" s="22" t="n">
+      <c r="C43" s="26" t="n">
         <v>1.9239</v>
       </c>
-      <c r="D43" s="23" t="inlineStr">
+      <c r="D43" s="27" t="inlineStr">
         <is>
           <t>arrive a3</t>
         </is>
       </c>
-      <c r="E43" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" s="21" t="n">
+      <c r="E43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K43" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="L43" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="21" t="n">
+      <c r="L43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="N43" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="P43" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q43" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="24" t="inlineStr">
-        <is>
-          <t>→ lab 2</t>
-        </is>
-      </c>
-      <c r="AA43" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB43" s="22" t="n">
-        <v>8.202698</v>
-      </c>
-      <c r="AC43" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="22" t="n">
-        <v>9.2027</v>
-      </c>
-      <c r="AE43" s="22" t="n">
-        <v>463.6989</v>
+      <c r="N43" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O43" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="P43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="28" t="inlineStr">
+        <is>
+          <t>no dispatch</t>
+        </is>
+      </c>
+      <c r="AA43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="26" t="n">
+        <v>12.152145</v>
+      </c>
+      <c r="AC43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="26" t="n">
+        <v>12.1521</v>
+      </c>
+      <c r="AE43" s="26" t="n">
+        <v>300958.8308</v>
       </c>
     </row>
     <row r="44" ht="13" customHeight="1">
@@ -4793,7 +4793,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>4</v>
@@ -4805,13 +4805,13 @@
         <v>4</v>
       </c>
       <c r="N44" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P44" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="9" t="n">
         <v>0</v>
@@ -4849,16 +4849,16 @@
         <v>0</v>
       </c>
       <c r="AB44" s="10" t="n">
-        <v>8.506501</v>
+        <v>12.759752</v>
       </c>
       <c r="AC44" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD44" s="10" t="n">
-        <v>8.506500000000001</v>
+        <v>12.7598</v>
       </c>
       <c r="AE44" s="10" t="n">
-        <v>472.2054</v>
+        <v>300971.5906</v>
       </c>
     </row>
     <row r="45" ht="13" customHeight="1">
@@ -4892,7 +4892,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K45" s="25" t="n">
         <v>4</v>
@@ -4904,258 +4904,258 @@
         <v>4</v>
       </c>
       <c r="N45" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O45" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="P45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="28" t="inlineStr">
+        <is>
+          <t>no dispatch</t>
+        </is>
+      </c>
+      <c r="AA45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="26" t="n">
+        <v>13.367359</v>
+      </c>
+      <c r="AC45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="26" t="n">
+        <v>13.3674</v>
+      </c>
+      <c r="AE45" s="26" t="n">
+        <v>300984.9579</v>
+      </c>
+    </row>
+    <row r="46" ht="13" customHeight="1">
+      <c r="A46" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" s="18" t="n">
+        <v>0.1011</v>
+      </c>
+      <c r="D46" s="19" t="inlineStr">
+        <is>
+          <t>arrive a3</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="P45" s="25" t="n">
+      <c r="L46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="N46" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="Q45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="28" t="inlineStr">
+      <c r="O46" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="P46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y46" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z46" s="20" t="inlineStr">
+        <is>
+          <t>→ lab 1</t>
+        </is>
+      </c>
+      <c r="AA46" s="18" t="n">
+        <v>146.81</v>
+      </c>
+      <c r="AB46" s="18" t="n">
+        <v>13.974967</v>
+      </c>
+      <c r="AC46" s="18" t="n">
+        <v>600000</v>
+      </c>
+      <c r="AD46" s="18" t="n">
+        <v>600160.785</v>
+      </c>
+      <c r="AE46" s="18" t="n">
+        <v>901145.7429</v>
+      </c>
+    </row>
+    <row r="47" ht="13" customHeight="1">
+      <c r="A47" s="29" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" s="30" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" s="31" t="inlineStr">
+        <is>
+          <t>proc L2</t>
+        </is>
+      </c>
+      <c r="E47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="M47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="O47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="32" t="inlineStr">
         <is>
           <t>no dispatch</t>
         </is>
       </c>
-      <c r="AA45" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" s="26" t="n">
-        <v>9.114108999999999</v>
-      </c>
-      <c r="AC45" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" s="26" t="n">
-        <v>9.114100000000001</v>
-      </c>
-      <c r="AE45" s="26" t="n">
-        <v>481.3195</v>
-      </c>
-    </row>
-    <row r="46" ht="13" customHeight="1">
-      <c r="A46" s="13" t="n">
-        <v>41</v>
-      </c>
-      <c r="B46" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C46" s="14" t="n">
-        <v>0.1011</v>
-      </c>
-      <c r="D46" s="15" t="inlineStr">
-        <is>
-          <t>arrive a3</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="K46" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="L46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="N46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="P46" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y46" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="16" t="inlineStr">
-        <is>
-          <t>→ lab 1</t>
-        </is>
-      </c>
-      <c r="AA46" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB46" s="14" t="n">
-        <v>9.721716000000001</v>
-      </c>
-      <c r="AC46" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD46" s="14" t="n">
-        <v>16.7217</v>
-      </c>
-      <c r="AE46" s="14" t="n">
-        <v>498.0413</v>
-      </c>
-    </row>
-    <row r="47" ht="13" customHeight="1">
-      <c r="A47" s="21" t="n">
-        <v>42</v>
-      </c>
-      <c r="B47" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="C47" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="D47" s="23" t="inlineStr">
-        <is>
-          <t>proc L2</t>
-        </is>
-      </c>
-      <c r="E47" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="21" t="n">
-        <v>7</v>
-      </c>
-      <c r="M47" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="O47" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="P47" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" s="24" t="inlineStr">
-        <is>
-          <t>→ lab 1</t>
-        </is>
-      </c>
-      <c r="AA47" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB47" s="22" t="n">
-        <v>10.329323</v>
-      </c>
-      <c r="AC47" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" s="22" t="n">
-        <v>11.3293</v>
-      </c>
-      <c r="AE47" s="22" t="n">
-        <v>509.3706</v>
+      <c r="AA47" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="30" t="n">
+        <v>11.848341</v>
+      </c>
+      <c r="AC47" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="30" t="n">
+        <v>11.8483</v>
+      </c>
+      <c r="AE47" s="30" t="n">
+        <v>901157.5912</v>
       </c>
     </row>
     <row r="48" ht="13" customHeight="1">
@@ -5186,7 +5186,7 @@
         <v>0</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="9" t="n">
         <v>0</v>
@@ -5201,10 +5201,10 @@
         <v>0</v>
       </c>
       <c r="N48" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P48" s="9" t="n">
         <v>0</v>
@@ -5245,16 +5245,16 @@
         <v>0</v>
       </c>
       <c r="AB48" s="10" t="n">
-        <v>8.202698</v>
+        <v>10.93693</v>
       </c>
       <c r="AC48" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD48" s="10" t="n">
-        <v>8.2027</v>
+        <v>10.9369</v>
       </c>
       <c r="AE48" s="10" t="n">
-        <v>517.5733</v>
+        <v>901168.5281999999</v>
       </c>
     </row>
     <row r="49" ht="13" customHeight="1">
@@ -5285,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="I49" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="29" t="n">
         <v>0</v>
@@ -5300,10 +5300,10 @@
         <v>0</v>
       </c>
       <c r="N49" s="29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O49" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P49" s="29" t="n">
         <v>0</v>
@@ -5344,16 +5344,16 @@
         <v>0</v>
       </c>
       <c r="AB49" s="30" t="n">
-        <v>7.595091</v>
+        <v>10.329323</v>
       </c>
       <c r="AC49" s="30" t="n">
         <v>0</v>
       </c>
       <c r="AD49" s="30" t="n">
-        <v>7.5951</v>
+        <v>10.3293</v>
       </c>
       <c r="AE49" s="30" t="n">
-        <v>525.1684</v>
+        <v>901178.8575</v>
       </c>
     </row>
     <row r="50" ht="13" customHeight="1">
@@ -5384,7 +5384,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="9" t="n">
         <v>0</v>
@@ -5399,159 +5399,159 @@
         <v>0</v>
       </c>
       <c r="N50" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="O50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="12" t="inlineStr">
+        <is>
+          <t>no dispatch</t>
+        </is>
+      </c>
+      <c r="AA50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="10" t="n">
+        <v>9.721716000000001</v>
+      </c>
+      <c r="AC50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="10" t="n">
+        <v>9.7217</v>
+      </c>
+      <c r="AE50" s="10" t="n">
+        <v>901188.5792</v>
+      </c>
+    </row>
+    <row r="51" ht="13" customHeight="1">
+      <c r="A51" s="29" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="O50" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="P50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" s="12" t="inlineStr">
+      <c r="C51" s="30" t="n">
+        <v>5.5696</v>
+      </c>
+      <c r="D51" s="31" t="inlineStr">
+        <is>
+          <t>arrive a3</t>
+        </is>
+      </c>
+      <c r="E51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="M51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="O51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="32" t="inlineStr">
         <is>
           <t>no dispatch</t>
         </is>
       </c>
-      <c r="AA50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" s="10" t="n">
-        <v>6.987483</v>
-      </c>
-      <c r="AC50" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" s="10" t="n">
-        <v>6.9875</v>
-      </c>
-      <c r="AE50" s="10" t="n">
-        <v>532.1559</v>
-      </c>
-    </row>
-    <row r="51" ht="13" customHeight="1">
-      <c r="A51" s="21" t="n">
-        <v>46</v>
-      </c>
-      <c r="B51" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="C51" s="22" t="n">
-        <v>5.5696</v>
-      </c>
-      <c r="D51" s="23" t="inlineStr">
-        <is>
-          <t>arrive a3</t>
-        </is>
-      </c>
-      <c r="E51" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="M51" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="O51" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="P51" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" s="24" t="inlineStr">
-        <is>
-          <t>→ lab 1</t>
-        </is>
-      </c>
-      <c r="AA51" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB51" s="22" t="n">
-        <v>7.595091</v>
-      </c>
-      <c r="AC51" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" s="22" t="n">
-        <v>8.5951</v>
-      </c>
-      <c r="AE51" s="22" t="n">
-        <v>540.7509</v>
+      <c r="AA51" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="30" t="n">
+        <v>10.329323</v>
+      </c>
+      <c r="AC51" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="30" t="n">
+        <v>10.3293</v>
+      </c>
+      <c r="AE51" s="30" t="n">
+        <v>901198.9085</v>
       </c>
     </row>
     <row r="52" ht="13" customHeight="1">
@@ -5582,10 +5582,10 @@
         <v>0</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>0</v>
@@ -5594,13 +5594,13 @@
         <v>5</v>
       </c>
       <c r="M52" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N52" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O52" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P52" s="9" t="n">
         <v>0</v>
@@ -5641,16 +5641,16 @@
         <v>0</v>
       </c>
       <c r="AB52" s="10" t="n">
-        <v>7.898894</v>
+        <v>10.93693</v>
       </c>
       <c r="AC52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD52" s="10" t="n">
-        <v>7.8989</v>
+        <v>10.9369</v>
       </c>
       <c r="AE52" s="10" t="n">
-        <v>548.6498</v>
+        <v>901209.8455000001</v>
       </c>
     </row>
     <row r="53" ht="13" customHeight="1">
@@ -5681,10 +5681,10 @@
         <v>0</v>
       </c>
       <c r="I53" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" s="29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K53" s="29" t="n">
         <v>0</v>
@@ -5693,13 +5693,13 @@
         <v>5</v>
       </c>
       <c r="M53" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" s="29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O53" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P53" s="29" t="n">
         <v>0</v>
@@ -5740,16 +5740,16 @@
         <v>0</v>
       </c>
       <c r="AB53" s="30" t="n">
-        <v>8.506501</v>
+        <v>11.544538</v>
       </c>
       <c r="AC53" s="30" t="n">
         <v>0</v>
       </c>
       <c r="AD53" s="30" t="n">
-        <v>8.506500000000001</v>
+        <v>11.5445</v>
       </c>
       <c r="AE53" s="30" t="n">
-        <v>557.1563</v>
+        <v>901221.39</v>
       </c>
     </row>
     <row r="54" ht="13" customHeight="1">
@@ -5780,10 +5780,10 @@
         <v>0</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K54" s="9" t="n">
         <v>0</v>
@@ -5792,13 +5792,13 @@
         <v>5</v>
       </c>
       <c r="M54" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O54" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P54" s="9" t="n">
         <v>0</v>
@@ -5813,10 +5813,10 @@
         <v>0</v>
       </c>
       <c r="T54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U54" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
         <v>0</v>
@@ -5839,16 +5839,16 @@
         <v>0</v>
       </c>
       <c r="AB54" s="10" t="n">
-        <v>9.114108999999999</v>
+        <v>12.152145</v>
       </c>
       <c r="AC54" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD54" s="10" t="n">
-        <v>9.114100000000001</v>
+        <v>12.1521</v>
       </c>
       <c r="AE54" s="10" t="n">
-        <v>566.2704</v>
+        <v>901233.5421</v>
       </c>
     </row>
     <row r="55" ht="13" customHeight="1">
@@ -5879,10 +5879,10 @@
         <v>0</v>
       </c>
       <c r="I55" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K55" s="29" t="n">
         <v>0</v>
@@ -5891,13 +5891,13 @@
         <v>5</v>
       </c>
       <c r="M55" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N55" s="29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O55" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P55" s="29" t="n">
         <v>0</v>
@@ -5938,16 +5938,16 @@
         <v>0</v>
       </c>
       <c r="AB55" s="30" t="n">
-        <v>8.202698</v>
+        <v>11.240734</v>
       </c>
       <c r="AC55" s="30" t="n">
         <v>0</v>
       </c>
       <c r="AD55" s="30" t="n">
-        <v>8.2027</v>
+        <v>11.2407</v>
       </c>
       <c r="AE55" s="30" t="n">
-        <v>574.4731</v>
+        <v>901244.7829</v>
       </c>
     </row>
     <row r="56" ht="13" customHeight="1">
@@ -5978,10 +5978,10 @@
         <v>0</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>0</v>
@@ -5990,13 +5990,13 @@
         <v>5</v>
       </c>
       <c r="M56" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O56" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P56" s="9" t="n">
         <v>0</v>
@@ -6037,16 +6037,16 @@
         <v>0</v>
       </c>
       <c r="AB56" s="10" t="n">
-        <v>8.810305</v>
+        <v>11.848341</v>
       </c>
       <c r="AC56" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD56" s="10" t="n">
-        <v>8.8103</v>
+        <v>11.8483</v>
       </c>
       <c r="AE56" s="10" t="n">
-        <v>583.2835</v>
+        <v>901256.6311999999</v>
       </c>
     </row>
     <row r="57" ht="13" customHeight="1">
@@ -6077,10 +6077,10 @@
         <v>0</v>
       </c>
       <c r="I57" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" s="29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K57" s="29" t="n">
         <v>0</v>
@@ -6089,13 +6089,13 @@
         <v>5</v>
       </c>
       <c r="M57" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N57" s="29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O57" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P57" s="29" t="n">
         <v>0</v>
@@ -6136,16 +6136,16 @@
         <v>0</v>
       </c>
       <c r="AB57" s="30" t="n">
-        <v>9.417911999999999</v>
+        <v>12.455948</v>
       </c>
       <c r="AC57" s="30" t="n">
         <v>0</v>
       </c>
       <c r="AD57" s="30" t="n">
-        <v>9.417899999999999</v>
+        <v>12.4559</v>
       </c>
       <c r="AE57" s="30" t="n">
-        <v>592.7014</v>
+        <v>901269.0872</v>
       </c>
     </row>
     <row r="58" ht="13" customHeight="1">
@@ -6176,10 +6176,10 @@
         <v>0</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K58" s="9" t="n">
         <v>0</v>
@@ -6188,13 +6188,13 @@
         <v>5</v>
       </c>
       <c r="M58" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O58" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P58" s="9" t="n">
         <v>0</v>
@@ -6203,10 +6203,10 @@
         <v>0</v>
       </c>
       <c r="R58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S58" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T58" s="9" t="n">
         <v>0</v>
@@ -6235,16 +6235,16 @@
         <v>0</v>
       </c>
       <c r="AB58" s="10" t="n">
-        <v>10.02552</v>
+        <v>13.063556</v>
       </c>
       <c r="AC58" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD58" s="10" t="n">
-        <v>10.0255</v>
+        <v>13.0636</v>
       </c>
       <c r="AE58" s="10" t="n">
-        <v>602.7269</v>
+        <v>901282.1507</v>
       </c>
     </row>
     <row r="59" ht="13" customHeight="1">
@@ -6275,10 +6275,10 @@
         <v>0</v>
       </c>
       <c r="I59" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K59" s="29" t="n">
         <v>0</v>
@@ -6287,13 +6287,13 @@
         <v>4</v>
       </c>
       <c r="M59" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N59" s="29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O59" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P59" s="29" t="n">
         <v>0</v>
@@ -6334,214 +6334,214 @@
         <v>0</v>
       </c>
       <c r="AB59" s="30" t="n">
-        <v>9.417911999999999</v>
+        <v>12.455948</v>
       </c>
       <c r="AC59" s="30" t="n">
         <v>0</v>
       </c>
       <c r="AD59" s="30" t="n">
-        <v>9.417899999999999</v>
+        <v>12.4559</v>
       </c>
       <c r="AE59" s="30" t="n">
-        <v>612.1448</v>
+        <v>901294.6067</v>
       </c>
     </row>
     <row r="60" ht="13" customHeight="1">
-      <c r="A60" s="13" t="n">
+      <c r="A60" s="17" t="n">
         <v>55</v>
       </c>
-      <c r="B60" s="13" t="n">
+      <c r="B60" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="C60" s="14" t="n">
+      <c r="C60" s="18" t="n">
         <v>0.1011</v>
       </c>
-      <c r="D60" s="15" t="inlineStr">
+      <c r="D60" s="19" t="inlineStr">
         <is>
           <t>proc L1</t>
         </is>
       </c>
-      <c r="E60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="13" t="n">
+      <c r="E60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="K60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="13" t="n">
+      <c r="K60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="M60" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N60" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="O60" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="P60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z60" s="16" t="inlineStr">
+      <c r="M60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z60" s="20" t="inlineStr">
+        <is>
+          <t>→ lab 2</t>
+        </is>
+      </c>
+      <c r="AA60" s="18" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="AB60" s="18" t="n">
+        <v>12.455948</v>
+      </c>
+      <c r="AC60" s="18" t="n">
+        <v>500000</v>
+      </c>
+      <c r="AD60" s="18" t="n">
+        <v>500060.3159</v>
+      </c>
+      <c r="AE60" s="18" t="n">
+        <v>1401354.9226</v>
+      </c>
+    </row>
+    <row r="61" ht="13" customHeight="1">
+      <c r="A61" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="B61" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C61" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
+          <t>arrive a3</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O61" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="P61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="16" t="inlineStr">
         <is>
           <t>no dispatch</t>
         </is>
       </c>
-      <c r="AA60" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB60" s="14" t="n">
-        <v>10.02552</v>
-      </c>
-      <c r="AC60" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD60" s="14" t="n">
-        <v>13.0255</v>
-      </c>
-      <c r="AE60" s="14" t="n">
-        <v>625.1703</v>
-      </c>
-    </row>
-    <row r="61" ht="13" customHeight="1">
-      <c r="A61" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="B61" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C61" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>arrive a3</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="8" t="inlineStr">
-        <is>
-          <t>no dispatch</t>
-        </is>
-      </c>
-      <c r="AA61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="6" t="n">
-        <v>13.671163</v>
-      </c>
-      <c r="AC61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="6" t="n">
-        <v>13.6712</v>
-      </c>
-      <c r="AE61" s="6" t="n">
-        <v>638.8415</v>
+      <c r="AA61" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="14" t="n">
+        <v>7.898894</v>
+      </c>
+      <c r="AC61" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="14" t="n">
+        <v>7.8989</v>
+      </c>
+      <c r="AE61" s="14" t="n">
+        <v>1401362.8215</v>
       </c>
     </row>
     <row r="62" ht="13" customHeight="1">
@@ -6572,7 +6572,7 @@
         <v>0</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J62" s="9" t="n">
         <v>1</v>
@@ -6581,165 +6581,165 @@
         <v>3</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="P62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="12" t="inlineStr">
+        <is>
+          <t>no dispatch</t>
+        </is>
+      </c>
+      <c r="AA62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="10" t="n">
+        <v>8.506501</v>
+      </c>
+      <c r="AC62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="10" t="n">
+        <v>8.506500000000001</v>
+      </c>
+      <c r="AE62" s="10" t="n">
+        <v>1401371.328</v>
+      </c>
+    </row>
+    <row r="63" ht="13" customHeight="1">
+      <c r="A63" s="13" t="n">
+        <v>58</v>
+      </c>
+      <c r="B63" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C63" s="14" t="n">
+        <v>6.7848</v>
+      </c>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>proc L1</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="O62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z62" s="12" t="inlineStr">
+      <c r="L63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="P63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="16" t="inlineStr">
         <is>
           <t>no dispatch</t>
         </is>
       </c>
-      <c r="AA62" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" s="10" t="n">
-        <v>14.27877</v>
-      </c>
-      <c r="AC62" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" s="10" t="n">
-        <v>14.2788</v>
-      </c>
-      <c r="AE62" s="10" t="n">
-        <v>653.1202</v>
-      </c>
-    </row>
-    <row r="63" ht="13" customHeight="1">
-      <c r="A63" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="B63" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C63" s="6" t="n">
-        <v>6.7848</v>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>proc L1</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K63" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z63" s="8" t="inlineStr">
-        <is>
-          <t>no dispatch</t>
-        </is>
-      </c>
-      <c r="AA63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB63" s="6" t="n">
-        <v>13.367359</v>
-      </c>
-      <c r="AC63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD63" s="6" t="n">
-        <v>13.3674</v>
-      </c>
-      <c r="AE63" s="6" t="n">
-        <v>666.4876</v>
+      <c r="AA63" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="14" t="n">
+        <v>7.595091</v>
+      </c>
+      <c r="AC63" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="14" t="n">
+        <v>7.5951</v>
+      </c>
+      <c r="AE63" s="14" t="n">
+        <v>1401378.9231</v>
       </c>
     </row>
     <row r="64" ht="13" customHeight="1">
@@ -6770,26 +6770,26 @@
         <v>0</v>
       </c>
       <c r="I64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="J64" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K64" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L64" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O64" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="P64" s="9" t="n">
         <v>0</v>
       </c>
@@ -6803,10 +6803,10 @@
         <v>0</v>
       </c>
       <c r="T64" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V64" s="9" t="n">
         <v>0</v>
@@ -6829,115 +6829,115 @@
         <v>0</v>
       </c>
       <c r="AB64" s="10" t="n">
-        <v>12.455948</v>
+        <v>6.68368</v>
       </c>
       <c r="AC64" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD64" s="10" t="n">
-        <v>12.4559</v>
+        <v>6.6837</v>
       </c>
       <c r="AE64" s="10" t="n">
-        <v>678.9435999999999</v>
+        <v>1401385.6068</v>
       </c>
     </row>
     <row r="65" ht="13" customHeight="1">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="B65" s="5" t="n">
+      <c r="B65" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C65" s="6" t="n">
+      <c r="C65" s="14" t="n">
         <v>5.5696</v>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D65" s="15" t="inlineStr">
         <is>
           <t>proc L2</t>
         </is>
       </c>
-      <c r="E65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="5" t="n">
+      <c r="E65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="J65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z65" s="8" t="inlineStr">
+      <c r="P65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="16" t="inlineStr">
         <is>
           <t>no dispatch</t>
         </is>
       </c>
-      <c r="AA65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB65" s="6" t="n">
-        <v>11.544538</v>
-      </c>
-      <c r="AC65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD65" s="6" t="n">
-        <v>11.5445</v>
-      </c>
-      <c r="AE65" s="6" t="n">
-        <v>690.4881</v>
+      <c r="AA65" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="14" t="n">
+        <v>5.772269</v>
+      </c>
+      <c r="AC65" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="14" t="n">
+        <v>5.7723</v>
+      </c>
+      <c r="AE65" s="14" t="n">
+        <v>1401391.3791</v>
       </c>
     </row>
     <row r="66" ht="13" customHeight="1">
@@ -6968,7 +6968,7 @@
         <v>0</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J66" s="9" t="n">
         <v>1</v>
@@ -6977,7 +6977,7 @@
         <v>1</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="9" t="n">
         <v>0</v>
@@ -6986,16 +6986,16 @@
         <v>0</v>
       </c>
       <c r="O66" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Q66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S66" s="9" t="n">
         <v>0</v>
@@ -7027,115 +7027,115 @@
         <v>0</v>
       </c>
       <c r="AB66" s="10" t="n">
-        <v>10.633127</v>
+        <v>5.164662</v>
       </c>
       <c r="AC66" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD66" s="10" t="n">
-        <v>10.6331</v>
+        <v>5.1647</v>
       </c>
       <c r="AE66" s="10" t="n">
-        <v>701.1212</v>
+        <v>1401396.5437</v>
       </c>
     </row>
     <row r="67" ht="13" customHeight="1">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="13" t="n">
         <v>62</v>
       </c>
-      <c r="B67" s="5" t="n">
+      <c r="B67" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C67" s="6" t="n">
+      <c r="C67" s="14" t="n">
         <v>4.3544</v>
       </c>
-      <c r="D67" s="7" t="inlineStr">
+      <c r="D67" s="15" t="inlineStr">
         <is>
           <t>proc L2</t>
         </is>
       </c>
-      <c r="E67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J67" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z67" s="8" t="inlineStr">
+      <c r="E67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="P67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="16" t="inlineStr">
         <is>
           <t>no dispatch</t>
         </is>
       </c>
-      <c r="AA67" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB67" s="6" t="n">
-        <v>9.721716000000001</v>
-      </c>
-      <c r="AC67" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD67" s="6" t="n">
-        <v>9.7217</v>
-      </c>
-      <c r="AE67" s="6" t="n">
-        <v>710.8429</v>
+      <c r="AA67" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" s="14" t="n">
+        <v>4.253251</v>
+      </c>
+      <c r="AC67" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" s="14" t="n">
+        <v>4.2533</v>
+      </c>
+      <c r="AE67" s="14" t="n">
+        <v>1401400.797</v>
       </c>
     </row>
     <row r="68" ht="13" customHeight="1">
@@ -7166,7 +7166,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J68" s="9" t="n">
         <v>1</v>
@@ -7175,7 +7175,7 @@
         <v>0</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="9" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>0</v>
       </c>
       <c r="O68" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P68" s="9" t="n">
         <v>0</v>
@@ -7193,7 +7193,7 @@
         <v>0</v>
       </c>
       <c r="R68" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68" s="9" t="n">
         <v>0</v>
@@ -7225,115 +7225,115 @@
         <v>0</v>
       </c>
       <c r="AB68" s="10" t="n">
-        <v>9.721716000000001</v>
+        <v>3.645643</v>
       </c>
       <c r="AC68" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD68" s="10" t="n">
-        <v>9.7217</v>
+        <v>3.6456</v>
       </c>
       <c r="AE68" s="10" t="n">
-        <v>720.5647</v>
+        <v>1401404.4426</v>
       </c>
     </row>
     <row r="69" ht="13" customHeight="1">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="B69" s="5" t="n">
+      <c r="B69" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C69" s="6" t="n">
+      <c r="C69" s="14" t="n">
         <v>3.1391</v>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D69" s="15" t="inlineStr">
         <is>
           <t>arrive a3</t>
         </is>
       </c>
-      <c r="E69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J69" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z69" s="8" t="inlineStr">
+      <c r="E69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="16" t="inlineStr">
         <is>
           <t>no dispatch</t>
         </is>
       </c>
-      <c r="AA69" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB69" s="6" t="n">
-        <v>9.114108999999999</v>
-      </c>
-      <c r="AC69" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD69" s="6" t="n">
-        <v>9.114100000000001</v>
-      </c>
-      <c r="AE69" s="6" t="n">
-        <v>729.6788</v>
+      <c r="AA69" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="14" t="n">
+        <v>3.645643</v>
+      </c>
+      <c r="AC69" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="14" t="n">
+        <v>3.6456</v>
+      </c>
+      <c r="AE69" s="14" t="n">
+        <v>1401408.0883</v>
       </c>
     </row>
     <row r="70" ht="13" customHeight="1">
@@ -7364,7 +7364,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J70" s="9" t="n">
         <v>2</v>
@@ -7382,7 +7382,7 @@
         <v>0</v>
       </c>
       <c r="O70" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P70" s="9" t="n">
         <v>0</v>
@@ -7423,115 +7423,115 @@
         <v>0</v>
       </c>
       <c r="AB70" s="10" t="n">
-        <v>9.721716000000001</v>
+        <v>4.253251</v>
       </c>
       <c r="AC70" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD70" s="10" t="n">
-        <v>9.7217</v>
+        <v>4.2533</v>
       </c>
       <c r="AE70" s="10" t="n">
-        <v>739.4005</v>
+        <v>1401412.3415</v>
       </c>
     </row>
     <row r="71" ht="13" customHeight="1">
-      <c r="A71" s="5" t="n">
+      <c r="A71" s="13" t="n">
         <v>66</v>
       </c>
-      <c r="B71" s="5" t="n">
+      <c r="B71" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C71" s="6" t="n">
+      <c r="C71" s="14" t="n">
         <v>1.9239</v>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D71" s="15" t="inlineStr">
         <is>
           <t>arrive a3</t>
         </is>
       </c>
-      <c r="E71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J71" s="5" t="n">
+      <c r="E71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="K71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z71" s="8" t="inlineStr">
+      <c r="K71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="16" t="inlineStr">
         <is>
           <t>no dispatch</t>
         </is>
       </c>
-      <c r="AA71" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB71" s="6" t="n">
-        <v>9.721716000000001</v>
-      </c>
-      <c r="AC71" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD71" s="6" t="n">
-        <v>9.7217</v>
-      </c>
-      <c r="AE71" s="6" t="n">
-        <v>749.1222</v>
+      <c r="AA71" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="14" t="n">
+        <v>4.253251</v>
+      </c>
+      <c r="AC71" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="14" t="n">
+        <v>4.2533</v>
+      </c>
+      <c r="AE71" s="14" t="n">
+        <v>1401416.5948</v>
       </c>
     </row>
     <row r="72" ht="13" customHeight="1">
@@ -7562,7 +7562,7 @@
         <v>0</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J72" s="9" t="n">
         <v>3</v>
@@ -7580,7 +7580,7 @@
         <v>0</v>
       </c>
       <c r="O72" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P72" s="9" t="n">
         <v>0</v>
@@ -7621,16 +7621,16 @@
         <v>0</v>
       </c>
       <c r="AB72" s="10" t="n">
-        <v>10.329323</v>
+        <v>4.860858</v>
       </c>
       <c r="AC72" s="10" t="n">
         <v>0</v>
       </c>
       <c r="AD72" s="10" t="n">
-        <v>10.3293</v>
+        <v>4.8609</v>
       </c>
       <c r="AE72" s="10" t="n">
-        <v>759.4515</v>
+        <v>1401421.4556</v>
       </c>
     </row>
     <row r="73" ht="13" customHeight="1">
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J73" s="5" t="n">
         <v>4</v>
@@ -7679,7 +7679,7 @@
         <v>0</v>
       </c>
       <c r="O73" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P73" s="5" t="n">
         <v>0</v>
@@ -7713,122 +7713,122 @@
       </c>
       <c r="Z73" s="8" t="inlineStr">
         <is>
+          <t>→ lab 1</t>
+        </is>
+      </c>
+      <c r="AA73" s="6" t="n">
+        <v>146.81</v>
+      </c>
+      <c r="AB73" s="6" t="n">
+        <v>5.468465</v>
+      </c>
+      <c r="AC73" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="6" t="n">
+        <v>152.2785</v>
+      </c>
+      <c r="AE73" s="6" t="n">
+        <v>1401573.7341</v>
+      </c>
+    </row>
+    <row r="74" ht="13" customHeight="1">
+      <c r="A74" s="17" t="n">
+        <v>69</v>
+      </c>
+      <c r="B74" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" s="18" t="n">
+        <v>0.1011</v>
+      </c>
+      <c r="D74" s="19" t="inlineStr">
+        <is>
+          <t>arrive a3</t>
+        </is>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="N74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="P74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="20" t="inlineStr">
+        <is>
           <t>no dispatch</t>
         </is>
       </c>
-      <c r="AA73" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB73" s="6" t="n">
-        <v>10.93693</v>
-      </c>
-      <c r="AC73" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD73" s="6" t="n">
-        <v>10.9369</v>
-      </c>
-      <c r="AE73" s="6" t="n">
-        <v>770.3884</v>
-      </c>
-    </row>
-    <row r="74" ht="13" customHeight="1">
-      <c r="A74" s="13" t="n">
-        <v>69</v>
-      </c>
-      <c r="B74" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="C74" s="14" t="n">
-        <v>0.1011</v>
-      </c>
-      <c r="D74" s="15" t="inlineStr">
-        <is>
-          <t>arrive a3</t>
-        </is>
-      </c>
-      <c r="E74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="J74" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="K74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y74" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z74" s="16" t="inlineStr">
-        <is>
-          <t>→ lab 1</t>
-        </is>
-      </c>
-      <c r="AA74" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB74" s="14" t="n">
-        <v>10.93693</v>
-      </c>
-      <c r="AC74" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD74" s="14" t="n">
-        <v>11.9369</v>
-      </c>
-      <c r="AE74" s="14" t="n">
-        <v>782.3253999999999</v>
+      <c r="AA74" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="18" t="n">
+        <v>3.949447</v>
+      </c>
+      <c r="AC74" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="18" t="n">
+        <v>3.9494</v>
+      </c>
+      <c r="AE74" s="18" t="n">
+        <v>1401577.6835</v>
       </c>
     </row>
   </sheetData>
@@ -7924,61 +7924,61 @@
       </c>
     </row>
     <row r="3" ht="14" customHeight="1">
-      <c r="A3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>3</v>
+      <c r="A3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="F3" s="35" t="n">
-        <v>4.5</v>
+        <v>200000</v>
       </c>
       <c r="G3" s="35" t="n">
-        <v>237.27</v>
+        <v>194.74</v>
       </c>
       <c r="H3" s="35" t="n">
-        <v>1</v>
+        <v>242.53</v>
       </c>
       <c r="I3" s="35" t="n">
-        <v>242.77</v>
+        <v>200437.27</v>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="17" t="n">
-        <v>0</v>
+      <c r="A4" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="F4" s="36" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G4" s="36" t="n">
-        <v>110.58</v>
+        <v>178.03</v>
       </c>
       <c r="H4" s="36" t="n">
-        <v>5</v>
+        <v>47.86</v>
       </c>
       <c r="I4" s="36" t="n">
-        <v>115.58</v>
+        <v>100225.89</v>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
@@ -7992,22 +7992,22 @@
         <v>4</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F5" s="37" t="n">
-        <v>6</v>
+        <v>600000</v>
       </c>
       <c r="G5" s="37" t="n">
-        <v>126.69</v>
+        <v>188.97</v>
       </c>
       <c r="H5" s="37" t="n">
-        <v>7</v>
+        <v>293.62</v>
       </c>
       <c r="I5" s="37" t="n">
-        <v>139.69</v>
+        <v>600482.59</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
@@ -8021,51 +8021,51 @@
         <v>0</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F6" s="38" t="n">
-        <v>3</v>
+        <v>500000</v>
       </c>
       <c r="G6" s="38" t="n">
-        <v>122.13</v>
+        <v>161.32</v>
       </c>
       <c r="H6" s="38" t="n">
-        <v>2</v>
+        <v>47.86</v>
       </c>
       <c r="I6" s="38" t="n">
-        <v>127.13</v>
+        <v>500209.18</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5" t="n">
+      <c r="B7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="35" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="35" t="n">
-        <v>156.16</v>
+        <v>75.95</v>
       </c>
       <c r="H7" s="35" t="n">
-        <v>1</v>
+        <v>146.81</v>
       </c>
       <c r="I7" s="35" t="n">
-        <v>157.16</v>
+        <v>222.76</v>
       </c>
     </row>
   </sheetData>
@@ -8147,13 +8147,13 @@
         </is>
       </c>
       <c r="D3" s="40" t="n">
-        <v>4.768428</v>
+        <v>1.754873</v>
       </c>
       <c r="E3" s="39" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="39" t="n">
-        <v>55.239945</v>
+        <v>132.954327</v>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
@@ -8171,13 +8171,13 @@
         </is>
       </c>
       <c r="D4" s="42" t="n">
-        <v>0.101741</v>
+        <v>0.744394</v>
       </c>
       <c r="E4" s="41" t="n">
         <v>3.3584</v>
       </c>
       <c r="F4" s="41" t="n">
-        <v>0.350947</v>
+        <v>16.792999</v>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
@@ -8195,13 +8195,13 @@
         </is>
       </c>
       <c r="D5" s="40" t="n">
-        <v>0.101569</v>
+        <v>0.743113</v>
       </c>
       <c r="E5" s="39" t="n">
         <v>2.2351</v>
       </c>
       <c r="F5" s="39" t="n">
-        <v>0.526437</v>
+        <v>25.189486</v>
       </c>
     </row>
     <row r="6" ht="14" customHeight="1">
@@ -8219,13 +8219,13 @@
         </is>
       </c>
       <c r="D6" s="42" t="n">
-        <v>0.050931</v>
+        <v>0.369941</v>
       </c>
       <c r="E6" s="41" t="n">
         <v>1.1125</v>
       </c>
       <c r="F6" s="41" t="n">
-        <v>0.53034</v>
+        <v>25.193098</v>
       </c>
     </row>
     <row r="7" ht="14" customHeight="1">
@@ -8243,13 +8243,13 @@
         </is>
       </c>
       <c r="D7" s="40" t="n">
-        <v>0.047188</v>
+        <v>0.315734</v>
       </c>
       <c r="E7" s="39" t="n">
         <v>0.554</v>
       </c>
       <c r="F7" s="39" t="n">
-        <v>0.986681</v>
+        <v>43.175954</v>
       </c>
     </row>
     <row r="8" ht="14" customHeight="1">
@@ -8267,13 +8267,13 @@
         </is>
       </c>
       <c r="D8" s="42" t="n">
-        <v>0.259478</v>
+        <v>0.516106</v>
       </c>
       <c r="E8" s="41" t="n">
         <v>4.4101</v>
       </c>
       <c r="F8" s="41" t="n">
-        <v>0.681603</v>
+        <v>8.866402000000001</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
@@ -8291,13 +8291,13 @@
         </is>
       </c>
       <c r="D9" s="40" t="n">
-        <v>0.355571</v>
+        <v>3.0717</v>
       </c>
       <c r="E9" s="39" t="n">
-        <v>3.282</v>
+        <v>212492.7993</v>
       </c>
       <c r="F9" s="39" t="n">
-        <v>1.255055</v>
+        <v>0.001095</v>
       </c>
     </row>
   </sheetData>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="B40" s="47" t="inlineStr">
         <is>
-          <t>[np.float64(1.0), np.float64(1.0)]</t>
+          <t>[np.float64(146.81), np.float64(47.86)]</t>
         </is>
       </c>
     </row>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="B41" s="45" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>125000.0</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="B42" s="47" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>100000.0</t>
         </is>
       </c>
     </row>
